--- a/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
+++ b/data_dictionaries/pt-BR/Belvo_Data_Dictionary_pt-BR.xlsx
@@ -32296,7 +32296,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>sooE7XJWEKypZJR603ecaWYk-8Ap0oD8Nr1pBQ4eG9c=</t>
+          <t>test_institution_user_id_1234567890abcdef123</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
